--- a/media/exports/reports/2025-12/callbacks.xlsx
+++ b/media/exports/reports/2025-12/callbacks.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="Called_back_within_2_working_hours_December">'Report'!$B$8</definedName>
-    <definedName name="Median_wait_December">'Report'!$B$9</definedName>
-    <definedName name="Enquiries_December">'Report'!$B$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$32</definedName>
+    <definedName name="Called_back_within_2_working_hours_December">'Report'!$B$9</definedName>
+    <definedName name="Median_wait_December">'Report'!$B$10</definedName>
+    <definedName name="Enquiries_December">'Report'!$B$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$53</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Data'!$A$1:$G$20</definedName>
@@ -55,6 +55,11 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
+      <color rgb="0025342A"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
@@ -75,11 +80,6 @@
     <font>
       <name val="Roboto"/>
       <color rgb="005F6F63"/>
-    </font>
-    <font>
-      <name val="Roboto"/>
-      <b val="1"/>
-      <color rgb="0025342A"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -117,36 +117,39 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -335,12 +338,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$14:$A$16</f>
+              <f>'Report'!$A$15:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$14:$B$16</f>
+              <f>'Report'!$B$15:$B$17</f>
             </numRef>
           </val>
         </ser>
@@ -489,7 +492,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2196000"/>
@@ -815,7 +818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -841,7 +844,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 6:28pm</t>
+          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -849,126 +852,132 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>In short: 70.6% called back within 2 working hours in December (target 80.0%); median wait 69 working minutes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>Every customer enquiry (phone, web form, email) and how long until someone first called back, in working minutes. Every call-out job has the enquiry that booked it.</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Called back within 2 working hours, December</t>
-        </is>
-      </c>
-      <c r="B8" s="6">
-        <f>Workings!B10</f>
-        <v/>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>target 80.0% · November 66.7%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Median wait, December</t>
-        </is>
-      </c>
-      <c r="B9" s="8">
-        <f>Workings!B17</f>
-        <v/>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>November 79 min (working minutes)</t>
+          <t>Called back within 2 working hours, December</t>
+        </is>
+      </c>
+      <c r="B9" s="7">
+        <f>Workings!B10</f>
+        <v/>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>target 80.0% · November 66.7%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Median wait, December</t>
+        </is>
+      </c>
+      <c r="B10" s="9">
+        <f>Workings!B16</f>
+        <v/>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>November 79 min (working minutes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Enquiries, December</t>
         </is>
       </c>
-      <c r="B10" s="8">
-        <f>Workings!B28</f>
-        <v/>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="B11" s="9">
+        <f>Workings!B25</f>
+        <v/>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>November 84</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Called back within 2 working hours, by channel, December 2025</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr"/>
-      <c r="B13" s="5" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Called back within 2 working hours</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="B14" s="6">
-        <f>Workings!B37</f>
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Web form</t>
-        </is>
-      </c>
-      <c r="B15" s="6">
-        <f>Workings!B45</f>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="B15" s="7">
+        <f>Workings!B37</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Web form</t>
+        </is>
+      </c>
+      <c r="B16" s="7">
+        <f>Workings!B45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="B16" s="6">
+      <c r="B17" s="7">
         <f>Workings!B53</f>
         <v/>
       </c>
     </row>
-    <row r="17"/>
     <row r="18"/>
     <row r="19"/>
     <row r="20"/>
@@ -977,64 +986,66 @@
     <row r="23"/>
     <row r="24"/>
     <row r="25"/>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Callbacks by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>70.6% of the 119 enquiries called back in December heard back within 2 working hours (target 80.0%), up from 66.7% in November. The median wait was 69 working minutes.</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>11 more enquiries would have needed a faster callback to reach the 80.0% target. Email enquiries are the slowest: 60.0% within 2 working hours.</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34"/>
+    <row r="35"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 callbacks.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 6:28pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 callbacks.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="27" min="0" max="16383" man="1"/>
+    <brk id="28" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1072,33 +1083,33 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 6:28pm</t>
+          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Callbacks within 2 working hours, December and November</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Within 2 working hours ÷ called back</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
@@ -1110,10 +1121,10 @@
           <t>Called back</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="14" t="n">
         <v>119</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="14" t="n">
         <v>84</v>
       </c>
     </row>
@@ -1123,24 +1134,24 @@
           <t>Within 2 working hours</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="14" t="n">
         <v>84</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="14" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="16">
         <f>B9/B8</f>
         <v/>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="16">
         <f>C9/C8</f>
         <v/>
       </c>
@@ -1148,27 +1159,27 @@
     <row r="11"/>
     <row r="12"/>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Median wait for a callback, December and November</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>The middle wait, in working minutes</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr"/>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
@@ -1180,23 +1191,23 @@
           <t>Median wait (working minutes)</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="14" t="n">
         <v>69</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="14" t="n">
         <v>79</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Enquiries called back</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>119</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>84</v>
       </c>
     </row>
@@ -1210,22 +1221,22 @@
     <row r="19"/>
     <row r="20"/>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Callbacks, Dec 25</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Enquiries called back within 2 working hours ÷ enquiries called back</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
@@ -1237,7 +1248,7 @@
           <t>Enquiries</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n">
+      <c r="B24" s="14" t="n">
         <v>119</v>
       </c>
     </row>
@@ -1247,7 +1258,7 @@
           <t>Called back</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n">
+      <c r="B25" s="14" t="n">
         <v>119</v>
       </c>
     </row>
@@ -1257,7 +1268,7 @@
           <t>Called back within 2 working hours</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n">
+      <c r="B26" s="14" t="n">
         <v>84</v>
       </c>
     </row>
@@ -1267,18 +1278,18 @@
           <t>Share within 2 working hours</t>
         </is>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="18">
         <f>B26/B25</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Median wait (working minutes)</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n">
+      <c r="B28" s="17" t="n">
         <v>69</v>
       </c>
     </row>
@@ -1292,22 +1303,22 @@
     <row r="30"/>
     <row r="31"/>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>Phone: callbacks, December 2025</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>Within 2 working hours ÷ called back</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr"/>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr"/>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
@@ -1319,7 +1330,7 @@
           <t>Called back</t>
         </is>
       </c>
-      <c r="B35" s="13" t="n">
+      <c r="B35" s="14" t="n">
         <v>74</v>
       </c>
     </row>
@@ -1329,17 +1340,17 @@
           <t>Within 2 working hours</t>
         </is>
       </c>
-      <c r="B36" s="13" t="n">
+      <c r="B36" s="14" t="n">
         <v>54</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="B37" s="15">
+      <c r="B37" s="16">
         <f>B36/B35</f>
         <v/>
       </c>
@@ -1347,22 +1358,22 @@
     <row r="38"/>
     <row r="39"/>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr">
+      <c r="A40" s="13" t="inlineStr">
         <is>
           <t>Web form: callbacks, December 2025</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>Within 2 working hours ÷ called back</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr"/>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr"/>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
@@ -1374,7 +1385,7 @@
           <t>Called back</t>
         </is>
       </c>
-      <c r="B43" s="13" t="n">
+      <c r="B43" s="14" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1384,17 +1395,17 @@
           <t>Within 2 working hours</t>
         </is>
       </c>
-      <c r="B44" s="13" t="n">
+      <c r="B44" s="14" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="14" t="inlineStr">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="B45" s="15">
+      <c r="B45" s="16">
         <f>B44/B43</f>
         <v/>
       </c>
@@ -1402,22 +1413,22 @@
     <row r="46"/>
     <row r="47"/>
     <row r="48">
-      <c r="A48" s="12" t="inlineStr">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>Email: callbacks, December 2025</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Within 2 working hours ÷ called back</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr"/>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr"/>
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
@@ -1429,7 +1440,7 @@
           <t>Called back</t>
         </is>
       </c>
-      <c r="B51" s="13" t="n">
+      <c r="B51" s="14" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1439,17 +1450,17 @@
           <t>Within 2 working hours</t>
         </is>
       </c>
-      <c r="B52" s="13" t="n">
+      <c r="B52" s="14" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="14" t="inlineStr">
+      <c r="A53" s="15" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="B53" s="15">
+      <c r="B53" s="16">
         <f>B52/B51</f>
         <v/>
       </c>
@@ -1463,7 +1474,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 callbacks.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 6:28pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 callbacks.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1555,465 +1566,465 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 6:28pm</t>
+          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Enquiries</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Called back</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Within 2 working hours</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Share within target</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Median wait (min)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="14" t="n">
         <v>96</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="14" t="n">
         <v>96</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="14" t="n">
         <v>83</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="18">
         <f>IF(D6=0,"",E6/D6)</f>
         <v/>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="14" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="14" t="n">
         <v>102</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="14" t="n">
         <v>102</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="14" t="n">
         <v>87</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="18">
         <f>IF(D7=0,"",E7/D7)</f>
         <v/>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="14" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="14" t="n">
         <v>121</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="14" t="n">
         <v>121</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="18">
         <f>IF(D8=0,"",E8/D8)</f>
         <v/>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="14" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="14" t="n">
         <v>117</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="14" t="n">
         <v>117</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="14" t="n">
         <v>93</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="18">
         <f>IF(D9=0,"",E9/D9)</f>
         <v/>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="14" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="14" t="n">
         <v>97</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="14" t="n">
         <v>97</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="14" t="n">
         <v>72</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="18">
         <f>IF(D10=0,"",E10/D10)</f>
         <v/>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="G10" s="14" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="14" t="n">
         <v>96</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="14" t="n">
         <v>96</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="18">
         <f>IF(D11=0,"",E11/D11)</f>
         <v/>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="14" t="n">
         <v>66</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="14" t="n">
         <v>90</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="14" t="n">
         <v>90</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="14" t="n">
         <v>64</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="18">
         <f>IF(D12=0,"",E12/D12)</f>
         <v/>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="G12" s="14" t="n">
         <v>71</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="14" t="n">
         <v>96</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="14" t="n">
         <v>96</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="14" t="n">
         <v>71</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="18">
         <f>IF(D13=0,"",E13/D13)</f>
         <v/>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="14" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C14" s="14" t="n">
         <v>94</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="14" t="n">
         <v>94</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="14" t="n">
         <v>64</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="18">
         <f>IF(D14=0,"",E14/D14)</f>
         <v/>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="G14" s="14" t="n">
         <v>72</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C15" s="14" t="n">
         <v>96</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="14" t="n">
         <v>96</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="14" t="n">
         <v>64</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="18">
         <f>IF(D15=0,"",E15/D15)</f>
         <v/>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="G15" s="14" t="n">
         <v>67</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="14" t="n">
         <v>98</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="14" t="n">
         <v>98</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="14" t="n">
         <v>65</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="18">
         <f>IF(D16=0,"",E16/D16)</f>
         <v/>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="G16" s="14" t="n">
         <v>76</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="14" t="n">
         <v>109</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="14" t="n">
         <v>109</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="14" t="n">
         <v>76</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="18">
         <f>IF(D17=0,"",E17/D17)</f>
         <v/>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="G17" s="14" t="n">
         <v>82</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="E18" s="13" t="n">
+      <c r="E18" s="14" t="n">
         <v>67</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="18">
         <f>IF(D18=0,"",E18/D18)</f>
         <v/>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="G18" s="14" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="14" t="n">
         <v>84</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="14" t="n">
         <v>84</v>
       </c>
-      <c r="E19" s="13" t="n">
+      <c r="E19" s="14" t="n">
         <v>56</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="18">
         <f>IF(D19=0,"",E19/D19)</f>
         <v/>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="G19" s="14" t="n">
         <v>79</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="C20" s="14" t="n">
         <v>119</v>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="14" t="n">
         <v>119</v>
       </c>
-      <c r="E20" s="13" t="n">
+      <c r="E20" s="14" t="n">
         <v>84</v>
       </c>
-      <c r="F20" s="17">
+      <c r="F20" s="18">
         <f>IF(D20=0,"",E20/D20)</f>
         <v/>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="G20" s="14" t="n">
         <v>69</v>
       </c>
     </row>
@@ -2023,7 +2034,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 callbacks.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 6:28pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 callbacks.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
